--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103841</v>
+        <v>103861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103861</v>
+        <v>103863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103863</v>
+        <v>103864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103864</v>
+        <v>103865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103897</v>
+        <v>103910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15903-2025 artfynd.xlsx
+++ b/artfynd/A 15903-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135876269</v>
       </c>
       <c r="B2" t="n">
-        <v>103910</v>
+        <v>103911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
